--- a/generation_zy/hiwo-任务1-1.xlsx
+++ b/generation_zy/hiwo-任务1-1.xlsx
@@ -1,53 +1,497 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3840" yWindow="2415" windowWidth="21555" windowHeight="10650" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="28800" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="任务参数配置" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="移液|||移液信息" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="任务参数配置" sheetId="1" r:id="rId3"/>
+    <sheet name="移液|||移液信息" sheetId="2" r:id="rId4"/>
+    <sheet name="Evaluation Warning" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>aa704df8-7966-4e05-8eda-5da0f5c56148</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>LiquidHandlerRoutineCmdInfo</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+  <si>
+    <t>*金属板编号</t>
+  </si>
+  <si>
+    <t>*任务名称</t>
+  </si>
+  <si>
+    <t>*工作流</t>
+  </si>
+  <si>
+    <t>*反应板条码</t>
+  </si>
+  <si>
+    <t>WF05</t>
+  </si>
+  <si>
+    <t>移液</t>
+  </si>
+  <si>
+    <t>B01-FY96</t>
+  </si>
+  <si>
+    <t>来源孔板条码</t>
+  </si>
+  <si>
+    <t>来源孔板列Y</t>
+  </si>
+  <si>
+    <t>目标孔板条码</t>
+  </si>
+  <si>
+    <t>目标孔板列Y</t>
+  </si>
+  <si>
+    <t>移液量(ul)</t>
+  </si>
+  <si>
+    <t>枪头库位</t>
+  </si>
+  <si>
+    <t>枪头列Y</t>
+  </si>
+  <si>
+    <t>mix次数</t>
+  </si>
+  <si>
+    <t>touching</t>
+  </si>
+  <si>
+    <t>金属板编号</t>
+  </si>
+  <si>
+    <t>A02-12</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>Evaluation Only. Created with Aspose.Cells for Python via .NET. Copyright 2003 - 2026 Aspose Pty Ltd.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
-    <font>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="18"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980008602142"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980008602142"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980008602142"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980008602142"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980008602142"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980008602142"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -55,177 +499,403 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499980002641678"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="54">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="54">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
+    <cellStyle name="千位分隔" xfId="6" builtinId="3"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="百分比" xfId="8" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="9" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="10" builtinId="7"/>
+    <cellStyle name="超链接" xfId="11" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="14" builtinId="11"/>
+    <cellStyle name="标题" xfId="15" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="16" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="17" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="18" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="19" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="20" builtinId="19"/>
+    <cellStyle name="输入" xfId="21" builtinId="20"/>
+    <cellStyle name="输出" xfId="22" builtinId="21"/>
+    <cellStyle name="计算" xfId="23" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="24" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="25" builtinId="24"/>
+    <cellStyle name="汇总" xfId="26" builtinId="25"/>
+    <cellStyle name="好" xfId="27" builtinId="26"/>
+    <cellStyle name="差" xfId="28" builtinId="27"/>
+    <cellStyle name="适中" xfId="29" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="30" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="31" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="32" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="33" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="34" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="36" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="37" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="38" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="39" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="40" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="41" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="42" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="43" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="45" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="46" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="47" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="48" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="49" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="50" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="51" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="52" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="53" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
+          <fgColor theme="4" tint="0.799979984760284"/>
+          <bgColor theme="4" tint="0.799979984760284"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
+          <fgColor theme="4" tint="0.799979984760284"/>
+          <bgColor theme="4" tint="0.799979984760284"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.7999511703848384"/>
-          <bgColor theme="4" tint="0.7999511703848384"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -236,7 +906,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -264,32 +934,149 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.3999450666829432"/>
+          <color theme="4" tint="0.399980008602142"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799979984760284"/>
+          <bgColor theme="4" tint="0.799979984760284"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399980008602142"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799979984760284"/>
+          <bgColor theme="4" tint="0.799979984760284"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399980008602142"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399980008602142"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799979984760284"/>
+          <bgColor theme="4" tint="0.799979984760284"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799979984760284"/>
+          <bgColor theme="4" tint="0.799979984760284"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799979984760284"/>
+          <bgColor theme="4" tint="0.799979984760284"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399980008602142"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399980008602142"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799979984760284"/>
+          <bgColor theme="4" tint="0.799979984760284"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399980008602142"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" table="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    <tableStyle name="PivotStylePreset2_Accent1" pivot="0" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -360,37 +1147,15 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>admin</author>
-  </authors>
-  <commentList>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>aa704df8-7966-4e05-8eda-5da0f5c56148</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>admin</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>LiquidHandlerRoutineCmdInfo</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -645,61 +1410,42 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.00428571428571" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="9"/>
+    <col min="1" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>*金属板编号</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>*任务名称</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>*工作流</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>*反应板条码</t>
-        </is>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>WF05</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>移液</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY96-B01</t>
-        </is>
+    <row r="2" ht="15"/>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -710,76 +1456,159 @@
     <mergeCell ref="D1:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultColWidth="9.00428571428571" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="10"/>
+    <col min="1" max="10" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>来源孔板条码</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>来源孔板列Y</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>目标孔板条码</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>目标孔板列Y</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>移液量(ul)</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>枪头库位</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>枪头列Y</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>mix次数</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>touching</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>金属板编号</t>
-        </is>
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>500</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1791BC96-7F58-4331-B626-963BDC0CBAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/generation_zy/hiwo-任务1-1.xlsx
+++ b/generation_zy/hiwo-任务1-1.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>*金属板编号</t>
   </si>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t>A02-12</t>
-  </si>
-  <si>
-    <t>A04</t>
   </si>
   <si>
     <t>A05</t>
@@ -1462,7 +1459,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="9.00428571428571" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="15" customWidth="1"/>
@@ -1514,13 +1511,13 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
@@ -1537,59 +1534,13 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4">
         <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>500</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1599,13 +1550,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1791BC96-7F58-4331-B626-963BDC0CBAA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7FF101-EF9C-464E-8659-A275A012BAA4}">
   <dimension ref="A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="5" spans="1:1" ht="23.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
